--- a/research/traditional_assets/database/data/bangladesh/bangladesh_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09470000000000001</v>
+        <v>0.009849999999999999</v>
       </c>
       <c r="E2">
-        <v>0.001999999999999988</v>
+        <v>-0.1625</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>28.9</v>
+        <v>11.34</v>
       </c>
       <c r="L2">
-        <v>0.1926666666666667</v>
+        <v>0.07042166056014407</v>
       </c>
       <c r="M2">
-        <v>15.263</v>
+        <v>21.473</v>
       </c>
       <c r="N2">
-        <v>0.01033798428610133</v>
+        <v>0.02375069129521071</v>
       </c>
       <c r="O2">
-        <v>0.5281314878892733</v>
+        <v>1.893562610229277</v>
       </c>
       <c r="P2">
-        <v>15.263</v>
+        <v>21.473</v>
       </c>
       <c r="Q2">
-        <v>0.01033798428610133</v>
+        <v>0.02375069129521071</v>
       </c>
       <c r="R2">
-        <v>0.5281314878892733</v>
+        <v>1.893562610229277</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>331</v>
+        <v>250.6</v>
       </c>
       <c r="V2">
-        <v>0.2241939853698185</v>
+        <v>0.2771817276849906</v>
       </c>
       <c r="W2">
-        <v>0.0382681323497676</v>
+        <v>0.04219906120868883</v>
       </c>
       <c r="X2">
-        <v>0.06227063992970769</v>
+        <v>0.1349899004677491</v>
       </c>
       <c r="Y2">
-        <v>-0.02400250757994009</v>
+        <v>-0.09279083925906031</v>
       </c>
       <c r="Z2">
-        <v>0.1577071483393437</v>
+        <v>0.1755171887602729</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05396155691391612</v>
+        <v>0.09894418280338303</v>
       </c>
       <c r="AC2">
-        <v>-0.05396155691391612</v>
+        <v>-0.09894418280338303</v>
       </c>
       <c r="AD2">
-        <v>614.6</v>
+        <v>582.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>614.6</v>
+        <v>582.9</v>
       </c>
       <c r="AG2">
-        <v>283.6</v>
+        <v>332.3</v>
       </c>
       <c r="AH2">
-        <v>0.2939263510282162</v>
+        <v>0.3919973100201748</v>
       </c>
       <c r="AI2">
-        <v>0.4666170642452587</v>
+        <v>0.4662826973842093</v>
       </c>
       <c r="AJ2">
-        <v>0.1611363636363637</v>
+        <v>0.2687641539954707</v>
       </c>
       <c r="AK2">
-        <v>0.2875859411442594</v>
+        <v>0.3324662331165582</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prime Finance &amp; Investment Limited (DSE:PRIMEFIN)</t>
+          <t>Investment Corporation of Bangladesh (DSE:ICB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,6 +709,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="E3">
+        <v>-0.214</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -722,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.28</v>
+        <v>20.9</v>
       </c>
       <c r="L3">
-        <v>0.6305418719211824</v>
+        <v>0.1804835924006908</v>
       </c>
       <c r="M3">
-        <v>0.263</v>
+        <v>15.1</v>
       </c>
       <c r="N3">
-        <v>0.005207920792079208</v>
+        <v>0.02094894561598224</v>
       </c>
       <c r="O3">
-        <v>0.20546875</v>
+        <v>0.722488038277512</v>
       </c>
       <c r="P3">
-        <v>0.263</v>
+        <v>15.1</v>
       </c>
       <c r="Q3">
-        <v>0.005207920792079208</v>
+        <v>0.02094894561598224</v>
       </c>
       <c r="R3">
-        <v>0.20546875</v>
+        <v>0.722488038277512</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11</v>
+        <v>124.8</v>
       </c>
       <c r="V3">
-        <v>0.2178217821782178</v>
+        <v>0.1731409544950056</v>
       </c>
       <c r="W3">
-        <v>0.04429065743944637</v>
+        <v>0.04010746497793129</v>
       </c>
       <c r="X3">
-        <v>0.05635799288739751</v>
+        <v>0.1098907323473432</v>
       </c>
       <c r="Y3">
-        <v>-0.01206733544795114</v>
+        <v>-0.0697832673694119</v>
       </c>
       <c r="Z3">
-        <v>0.05202460276781138</v>
+        <v>0.1663554087056457</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05248894401547884</v>
+        <v>0.09556153692079042</v>
       </c>
       <c r="AC3">
-        <v>-0.05248894401547884</v>
+        <v>-0.09556153692079042</v>
       </c>
       <c r="AD3">
-        <v>15.1</v>
+        <v>304.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.1</v>
+        <v>304.4</v>
       </c>
       <c r="AG3">
-        <v>4.1</v>
+        <v>179.6</v>
       </c>
       <c r="AH3">
-        <v>0.2301829268292683</v>
+        <v>0.2969176746000781</v>
       </c>
       <c r="AI3">
-        <v>0.25</v>
+        <v>0.3645508982035928</v>
       </c>
       <c r="AJ3">
-        <v>0.07509157509157509</v>
+        <v>0.1994669035984007</v>
       </c>
       <c r="AK3">
-        <v>0.08299595141700404</v>
+        <v>0.2528865108420162</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -817,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Investment Corporation of Bangladesh (DSE:ICB)</t>
+          <t>Prime Finance &amp; Investment Limited (DSE:PRIMEFIN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -825,12 +831,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.1</v>
-      </c>
-      <c r="E4">
-        <v>-0.165</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -844,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>16.7</v>
+        <v>1.28</v>
       </c>
       <c r="L4">
-        <v>0.1591992373689228</v>
+        <v>0.6305418719211824</v>
       </c>
       <c r="M4">
-        <v>3.3</v>
+        <v>0.263</v>
       </c>
       <c r="N4">
-        <v>0.002819789797487824</v>
+        <v>0.008622950819672131</v>
       </c>
       <c r="O4">
-        <v>0.1976047904191617</v>
+        <v>0.20546875</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>0.263</v>
       </c>
       <c r="Q4">
-        <v>0.002819789797487824</v>
+        <v>0.008622950819672131</v>
       </c>
       <c r="R4">
-        <v>0.1976047904191617</v>
+        <v>0.20546875</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>145.9</v>
+        <v>11</v>
       </c>
       <c r="V4">
-        <v>0.1246688883192344</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="W4">
-        <v>0.03224560726008882</v>
+        <v>0.04429065743944637</v>
       </c>
       <c r="X4">
-        <v>0.056729618386941</v>
+        <v>0.1126082147011522</v>
       </c>
       <c r="Y4">
-        <v>-0.02448401112685217</v>
+        <v>-0.06831755726170582</v>
       </c>
       <c r="Z4">
-        <v>0.147310770959135</v>
+        <v>0.05202460276781138</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05261373603498776</v>
+        <v>0.09744867277260993</v>
       </c>
       <c r="AC4">
-        <v>-0.05261373603498776</v>
+        <v>-0.09744867277260993</v>
       </c>
       <c r="AD4">
-        <v>368.7</v>
+        <v>15.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>368.7</v>
+        <v>15.1</v>
       </c>
       <c r="AG4">
-        <v>222.8</v>
+        <v>4.1</v>
       </c>
       <c r="AH4">
-        <v>0.2395711500974659</v>
+        <v>0.331140350877193</v>
       </c>
       <c r="AI4">
-        <v>0.4105790645879733</v>
+        <v>0.25</v>
       </c>
       <c r="AJ4">
-        <v>0.159931088938339</v>
+        <v>0.1184971098265896</v>
       </c>
       <c r="AK4">
-        <v>0.2962372024996676</v>
+        <v>0.08299595141700404</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08939999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="E5">
-        <v>0.169</v>
+        <v>-0.111</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -966,28 +966,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>16.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L5">
-        <v>0.3563714902807776</v>
+        <v>0.1935185185185185</v>
       </c>
       <c r="M5">
-        <v>11.7</v>
+        <v>6.11</v>
       </c>
       <c r="N5">
-        <v>0.04966044142614601</v>
+        <v>0.04486049926578561</v>
       </c>
       <c r="O5">
-        <v>0.709090909090909</v>
+        <v>0.7308612440191389</v>
       </c>
       <c r="P5">
-        <v>11.7</v>
+        <v>6.11</v>
       </c>
       <c r="Q5">
-        <v>0.04966044142614601</v>
+        <v>0.04486049926578561</v>
       </c>
       <c r="R5">
-        <v>0.709090909090909</v>
+        <v>0.7308612440191389</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -996,55 +996,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>160.1</v>
+        <v>103.5</v>
       </c>
       <c r="V5">
-        <v>0.6795415959252971</v>
+        <v>0.7599118942731278</v>
       </c>
       <c r="W5">
-        <v>0.1458885941644562</v>
+        <v>0.06858080393765381</v>
       </c>
       <c r="X5">
-        <v>0.06781166147247439</v>
+        <v>0.1573715862343461</v>
       </c>
       <c r="Y5">
-        <v>0.07807693269198185</v>
+        <v>-0.08879078229669227</v>
       </c>
       <c r="Z5">
-        <v>0.2904642409033876</v>
+        <v>0.2905178211163416</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05530937779284446</v>
+        <v>0.1004396928341561</v>
       </c>
       <c r="AC5">
-        <v>-0.05530937779284446</v>
+        <v>-0.1004396928341561</v>
       </c>
       <c r="AD5">
-        <v>186.9</v>
+        <v>230.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>186.9</v>
+        <v>230.7</v>
       </c>
       <c r="AG5">
-        <v>26.80000000000001</v>
+        <v>127.2</v>
       </c>
       <c r="AH5">
-        <v>0.4423668639053255</v>
+        <v>0.6287816843826656</v>
       </c>
       <c r="AI5">
-        <v>0.600771456123433</v>
+        <v>0.6825443786982248</v>
       </c>
       <c r="AJ5">
-        <v>0.1021341463414635</v>
+        <v>0.4829157175398633</v>
       </c>
       <c r="AK5">
-        <v>0.1774834437086094</v>
+        <v>0.5424307036247334</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1069,23 +1069,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G6">
-        <v>-0</v>
-      </c>
-      <c r="H6">
-        <v>-0</v>
-      </c>
-      <c r="I6">
-        <v>-0</v>
-      </c>
-      <c r="J6">
-        <v>-0</v>
-      </c>
       <c r="K6">
-        <v>-5.58</v>
-      </c>
-      <c r="L6">
-        <v>1.727554179566563</v>
+        <v>-19.2</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1109,55 +1094,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>11.3</v>
       </c>
       <c r="V6">
-        <v>0.7</v>
+        <v>0.6807228915662651</v>
       </c>
       <c r="W6">
-        <v>-0.5993555316863587</v>
+        <v>-5.133689839572192</v>
       </c>
       <c r="X6">
-        <v>0.100292351003155</v>
+        <v>0.1676796440278646</v>
       </c>
       <c r="Y6">
-        <v>-0.6996478826895137</v>
+        <v>-5.301369483600056</v>
       </c>
       <c r="Z6">
-        <v>-0.07953705983747845</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05856128491825337</v>
+        <v>0.1007864293278408</v>
       </c>
       <c r="AC6">
-        <v>-0.05856128491825337</v>
+        <v>-0.1007864293278408</v>
       </c>
       <c r="AD6">
-        <v>43.9</v>
+        <v>32.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>43.9</v>
+        <v>32.7</v>
       </c>
       <c r="AG6">
-        <v>29.9</v>
+        <v>21.4</v>
       </c>
       <c r="AH6">
-        <v>0.6870109546165885</v>
+        <v>0.6632860040567952</v>
       </c>
       <c r="AI6">
-        <v>0.9214945424013433</v>
+        <v>1.958083832335329</v>
       </c>
       <c r="AJ6">
-        <v>0.5991983967935872</v>
+        <v>0.5631578947368422</v>
       </c>
       <c r="AK6">
-        <v>0.8888228299643282</v>
+        <v>3.962962962962962</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.009849999999999999</v>
-      </c>
-      <c r="E2">
-        <v>-0.1625</v>
+        <v>-0.298</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +603,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11.34</v>
+        <v>-38.1</v>
       </c>
       <c r="L2">
-        <v>0.07042166056014407</v>
+        <v>-3.81</v>
       </c>
       <c r="M2">
-        <v>21.473</v>
+        <v>3.44</v>
       </c>
       <c r="N2">
-        <v>0.02375069129521071</v>
+        <v>0.004986952739924616</v>
       </c>
       <c r="O2">
-        <v>1.893562610229277</v>
+        <v>-0.09028871391076115</v>
       </c>
       <c r="P2">
-        <v>21.473</v>
+        <v>3.44</v>
       </c>
       <c r="Q2">
-        <v>0.02375069129521071</v>
+        <v>0.004986952739924616</v>
       </c>
       <c r="R2">
-        <v>1.893562610229277</v>
+        <v>-0.09028871391076115</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>250.6</v>
+        <v>111.1</v>
       </c>
       <c r="V2">
-        <v>0.2771817276849906</v>
+        <v>0.1610611771527979</v>
       </c>
       <c r="W2">
-        <v>0.04219906120868883</v>
+        <v>0.663033638801967</v>
       </c>
       <c r="X2">
-        <v>0.1349899004677491</v>
+        <v>0.1180832132207194</v>
       </c>
       <c r="Y2">
-        <v>-0.09279083925906031</v>
+        <v>0.5449504255812475</v>
       </c>
       <c r="Z2">
-        <v>0.1755171887602729</v>
+        <v>0.01727115716753023</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09894418280338303</v>
+        <v>0.09059803855148649</v>
       </c>
       <c r="AC2">
-        <v>-0.09894418280338303</v>
+        <v>-0.09059803855148649</v>
       </c>
       <c r="AD2">
-        <v>582.9</v>
+        <v>240.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>582.9</v>
+        <v>240.8</v>
       </c>
       <c r="AG2">
-        <v>332.3</v>
+        <v>129.7</v>
       </c>
       <c r="AH2">
-        <v>0.3919973100201748</v>
+        <v>0.2587577906726843</v>
       </c>
       <c r="AI2">
-        <v>0.4662826973842093</v>
+        <v>0.40600236047884</v>
       </c>
       <c r="AJ2">
-        <v>0.2687641539954707</v>
+        <v>0.1582672361195851</v>
       </c>
       <c r="AK2">
-        <v>0.3324662331165582</v>
+        <v>0.2690871369294606</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +707,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.005699999999999999</v>
-      </c>
-      <c r="E3">
-        <v>-0.214</v>
+        <v>-0.298</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +722,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>20.9</v>
+        <v>-16.3</v>
       </c>
       <c r="L3">
-        <v>0.1804835924006908</v>
+        <v>-1.63</v>
       </c>
       <c r="M3">
-        <v>15.1</v>
+        <v>3.44</v>
       </c>
       <c r="N3">
-        <v>0.02094894561598224</v>
+        <v>0.00508574807806032</v>
       </c>
       <c r="O3">
-        <v>0.722488038277512</v>
+        <v>-0.211042944785276</v>
       </c>
       <c r="P3">
-        <v>15.1</v>
+        <v>3.44</v>
       </c>
       <c r="Q3">
-        <v>0.02094894561598224</v>
+        <v>0.00508574807806032</v>
       </c>
       <c r="R3">
-        <v>0.722488038277512</v>
+        <v>-0.211042944785276</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>124.8</v>
+        <v>97</v>
       </c>
       <c r="V3">
-        <v>0.1731409544950056</v>
+        <v>0.1434062684801893</v>
       </c>
       <c r="W3">
-        <v>0.04010746497793129</v>
+        <v>-0.03643272239606617</v>
       </c>
       <c r="X3">
-        <v>0.1098907323473432</v>
+        <v>0.09164806194690409</v>
       </c>
       <c r="Y3">
-        <v>-0.0697832673694119</v>
+        <v>-0.1280807843429703</v>
       </c>
       <c r="Z3">
-        <v>0.1663554087056457</v>
+        <v>0.01743375174337518</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09556153692079042</v>
+        <v>0.08689024964906195</v>
       </c>
       <c r="AC3">
-        <v>-0.09556153692079042</v>
+        <v>-0.08689024964906195</v>
       </c>
       <c r="AD3">
-        <v>304.4</v>
+        <v>213.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>304.4</v>
+        <v>213.2</v>
       </c>
       <c r="AG3">
-        <v>179.6</v>
+        <v>116.2</v>
       </c>
       <c r="AH3">
-        <v>0.2969176746000781</v>
+        <v>0.239658273381295</v>
       </c>
       <c r="AI3">
-        <v>0.3645508982035928</v>
+        <v>0.3541528239202658</v>
       </c>
       <c r="AJ3">
-        <v>0.1994669035984007</v>
+        <v>0.1466061064849861</v>
       </c>
       <c r="AK3">
-        <v>0.2528865108420162</v>
+        <v>0.2300990099009901</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prime Finance &amp; Investment Limited (DSE:PRIMEFIN)</t>
+          <t>Union Capital Limited (DSE:UNIONCAP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,323 +825,85 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
-        <v>1.28</v>
-      </c>
-      <c r="L4">
-        <v>0.6305418719211824</v>
+        <v>-21.8</v>
       </c>
       <c r="M4">
-        <v>0.263</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.008622950819672131</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.20546875</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.263</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.008622950819672131</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.20546875</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>11</v>
+        <v>14.1</v>
       </c>
       <c r="V4">
-        <v>0.360655737704918</v>
+        <v>1.052238805970149</v>
       </c>
       <c r="W4">
-        <v>0.04429065743944637</v>
+        <v>1.3625</v>
       </c>
       <c r="X4">
-        <v>0.1126082147011522</v>
+        <v>0.1445183644945348</v>
       </c>
       <c r="Y4">
-        <v>-0.06831755726170582</v>
+        <v>1.217981635505465</v>
       </c>
       <c r="Z4">
-        <v>0.05202460276781138</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09744867277260993</v>
+        <v>0.09430582745391103</v>
       </c>
       <c r="AC4">
-        <v>-0.09744867277260993</v>
+        <v>-0.09430582745391103</v>
       </c>
       <c r="AD4">
-        <v>15.1</v>
+        <v>27.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15.1</v>
+        <v>27.6</v>
       </c>
       <c r="AG4">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>0.331140350877193</v>
+        <v>0.6731707317073171</v>
       </c>
       <c r="AI4">
-        <v>0.25</v>
+        <v>-3.101123595505618</v>
       </c>
       <c r="AJ4">
-        <v>0.1184971098265896</v>
+        <v>0.5018587360594796</v>
       </c>
       <c r="AK4">
-        <v>0.08299595141700404</v>
+        <v>-0.5869565217391305</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LankaBangla Finance Limited (DSE:LANKABAFIN)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.014</v>
-      </c>
-      <c r="E5">
-        <v>-0.111</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="L5">
-        <v>0.1935185185185185</v>
-      </c>
-      <c r="M5">
-        <v>6.11</v>
-      </c>
-      <c r="N5">
-        <v>0.04486049926578561</v>
-      </c>
-      <c r="O5">
-        <v>0.7308612440191389</v>
-      </c>
-      <c r="P5">
-        <v>6.11</v>
-      </c>
-      <c r="Q5">
-        <v>0.04486049926578561</v>
-      </c>
-      <c r="R5">
-        <v>0.7308612440191389</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>103.5</v>
-      </c>
-      <c r="V5">
-        <v>0.7599118942731278</v>
-      </c>
-      <c r="W5">
-        <v>0.06858080393765381</v>
-      </c>
-      <c r="X5">
-        <v>0.1573715862343461</v>
-      </c>
-      <c r="Y5">
-        <v>-0.08879078229669227</v>
-      </c>
-      <c r="Z5">
-        <v>0.2905178211163416</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.1004396928341561</v>
-      </c>
-      <c r="AC5">
-        <v>-0.1004396928341561</v>
-      </c>
-      <c r="AD5">
-        <v>230.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>230.7</v>
-      </c>
-      <c r="AG5">
-        <v>127.2</v>
-      </c>
-      <c r="AH5">
-        <v>0.6287816843826656</v>
-      </c>
-      <c r="AI5">
-        <v>0.6825443786982248</v>
-      </c>
-      <c r="AJ5">
-        <v>0.4829157175398633</v>
-      </c>
-      <c r="AK5">
-        <v>0.5424307036247334</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Union Capital Limited (DSE:UNIONCAP)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>-19.2</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>11.3</v>
-      </c>
-      <c r="V6">
-        <v>0.6807228915662651</v>
-      </c>
-      <c r="W6">
-        <v>-5.133689839572192</v>
-      </c>
-      <c r="X6">
-        <v>0.1676796440278646</v>
-      </c>
-      <c r="Y6">
-        <v>-5.301369483600056</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.1007864293278408</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1007864293278408</v>
-      </c>
-      <c r="AD6">
-        <v>32.7</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>32.7</v>
-      </c>
-      <c r="AG6">
-        <v>21.4</v>
-      </c>
-      <c r="AH6">
-        <v>0.6632860040567952</v>
-      </c>
-      <c r="AI6">
-        <v>1.958083832335329</v>
-      </c>
-      <c r="AJ6">
-        <v>0.5631578947368422</v>
-      </c>
-      <c r="AK6">
-        <v>3.962962962962962</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>
